--- a/data/demo/Product_Master.xlsx
+++ b/data/demo/Product_Master.xlsx
@@ -8,14 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/michaelcillo/GitHub Repos/inventory-analytics-dashboard/data/demo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B64BD3-0B1C-304C-8868-47AA136C3F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B166E6-03BE-4746-8153-6E4B78D764B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="41120" windowHeight="24620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$76</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -978,13 +994,18 @@
   <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="6.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.1640625" customWidth="1"/>
-    <col min="5" max="5" width="9.83203125" customWidth="1"/>
-    <col min="6" max="8" width="18" customWidth="1"/>
-    <col min="9" max="12" width="15" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15">
@@ -2998,7 +3019,7 @@
         <v>11</v>
       </c>
       <c r="L53" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3872,10 +3893,11 @@
         <v>11</v>
       </c>
       <c r="L76" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L76" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataValidations count="1">
     <dataValidation type="list" sqref="J2:L76" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Y,N"</formula1>
